--- a/public/exports-60-250/29189560.xlsx
+++ b/public/exports-60-250/29189560.xlsx
@@ -10564,7 +10564,7 @@
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t xml:space="preserve">311235937</t>
+          <t xml:space="preserve">311235933</t>
         </is>
       </c>
       <c r="L141" t="inlineStr">
@@ -10639,7 +10639,7 @@
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t xml:space="preserve">311235937</t>
+          <t xml:space="preserve">311235933</t>
         </is>
       </c>
       <c r="L142" t="inlineStr">
@@ -10714,7 +10714,7 @@
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t xml:space="preserve">311235937</t>
+          <t xml:space="preserve">311235933</t>
         </is>
       </c>
       <c r="L143" t="inlineStr">
